--- a/artfynd/A 14927-2023 artfynd.xlsx
+++ b/artfynd/A 14927-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 14927-2023 artfynd.xlsx
+++ b/artfynd/A 14927-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1480,6 +1480,363 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129224538</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58093</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>752678</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7093588</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129224522</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57720</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>752490</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7093754</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>Tallhögstubbe</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Tallhögstubbe</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129224541</v>
+      </c>
+      <c r="B11" t="n">
+        <v>56904</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>752559</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7093660</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Stöttes, flög iväg</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 14927-2023 artfynd.xlsx
+++ b/artfynd/A 14927-2023 artfynd.xlsx
@@ -1485,7 +1485,7 @@
         <v>129224538</v>
       </c>
       <c r="B9" t="n">
-        <v>58093</v>
+        <v>58095</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>129224522</v>
       </c>
       <c r="B10" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>129224541</v>
       </c>
       <c r="B11" t="n">
-        <v>56904</v>
+        <v>56906</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 14927-2023 artfynd.xlsx
+++ b/artfynd/A 14927-2023 artfynd.xlsx
@@ -1482,27 +1482,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129224538</v>
+        <v>129224522</v>
       </c>
       <c r="B9" t="n">
-        <v>58095</v>
+        <v>57722</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1510,14 +1510,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1526,10 +1522,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>752678</v>
+        <v>752490</v>
       </c>
       <c r="R9" t="n">
-        <v>7093588</v>
+        <v>7093754</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1564,11 +1560,6 @@
           <t>2025-10-19</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>13:50</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1577,6 +1568,26 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>Tallhögstubbe</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Tallhögstubbe</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1593,27 +1604,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129224522</v>
+        <v>129224538</v>
       </c>
       <c r="B10" t="n">
-        <v>57722</v>
+        <v>58095</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1621,10 +1632,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1633,10 +1648,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>752490</v>
+        <v>752678</v>
       </c>
       <c r="R10" t="n">
-        <v>7093754</v>
+        <v>7093588</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1671,6 +1686,11 @@
           <t>2025-10-19</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1679,26 +1699,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>Tallhögstubbe</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Tallhögstubbe</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">

--- a/artfynd/A 14927-2023 artfynd.xlsx
+++ b/artfynd/A 14927-2023 artfynd.xlsx
@@ -1485,7 +1485,7 @@
         <v>129224522</v>
       </c>
       <c r="B9" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>129224538</v>
       </c>
       <c r="B10" t="n">
-        <v>58095</v>
+        <v>58097</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>129224541</v>
       </c>
       <c r="B11" t="n">
-        <v>56906</v>
+        <v>56908</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 14927-2023 artfynd.xlsx
+++ b/artfynd/A 14927-2023 artfynd.xlsx
@@ -1482,27 +1482,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129224522</v>
+        <v>129224538</v>
       </c>
       <c r="B9" t="n">
-        <v>57724</v>
+        <v>58097</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1510,10 +1510,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1522,10 +1526,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>752490</v>
+        <v>752678</v>
       </c>
       <c r="R9" t="n">
-        <v>7093754</v>
+        <v>7093588</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1560,6 +1564,11 @@
           <t>2025-10-19</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1568,26 +1577,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>Tallhögstubbe</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Tallhögstubbe</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1604,27 +1593,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129224538</v>
+        <v>129224522</v>
       </c>
       <c r="B10" t="n">
-        <v>58097</v>
+        <v>57724</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1632,14 +1621,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1648,10 +1633,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>752678</v>
+        <v>752490</v>
       </c>
       <c r="R10" t="n">
-        <v>7093588</v>
+        <v>7093754</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1686,11 +1671,6 @@
           <t>2025-10-19</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>13:50</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1699,6 +1679,26 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>Tallhögstubbe</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Tallhögstubbe</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">

--- a/artfynd/A 14927-2023 artfynd.xlsx
+++ b/artfynd/A 14927-2023 artfynd.xlsx
@@ -1482,27 +1482,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129224538</v>
+        <v>129224522</v>
       </c>
       <c r="B9" t="n">
-        <v>58097</v>
+        <v>57724</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1510,14 +1510,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1526,10 +1522,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>752678</v>
+        <v>752490</v>
       </c>
       <c r="R9" t="n">
-        <v>7093588</v>
+        <v>7093754</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1564,11 +1560,6 @@
           <t>2025-10-19</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>13:50</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1577,6 +1568,26 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>Tallhögstubbe</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Tallhögstubbe</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1593,27 +1604,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129224522</v>
+        <v>129224538</v>
       </c>
       <c r="B10" t="n">
-        <v>57724</v>
+        <v>58097</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1621,10 +1632,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1633,10 +1648,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>752490</v>
+        <v>752678</v>
       </c>
       <c r="R10" t="n">
-        <v>7093754</v>
+        <v>7093588</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1671,6 +1686,11 @@
           <t>2025-10-19</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1679,26 +1699,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>Tallhögstubbe</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Tallhögstubbe</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">

--- a/artfynd/A 14927-2023 artfynd.xlsx
+++ b/artfynd/A 14927-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>108660302</v>
       </c>
       <c r="B2" t="n">
-        <v>57064</v>
+        <v>57066</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 14927-2023 artfynd.xlsx
+++ b/artfynd/A 14927-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>108660302</v>
       </c>
       <c r="B2" t="n">
-        <v>57066</v>
+        <v>57067</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 14927-2023 artfynd.xlsx
+++ b/artfynd/A 14927-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>108660302</v>
       </c>
       <c r="B2" t="n">
-        <v>57067</v>
+        <v>57070</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 14927-2023 artfynd.xlsx
+++ b/artfynd/A 14927-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>108660302</v>
       </c>
       <c r="B2" t="n">
-        <v>57070</v>
+        <v>57071</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
